--- a/data/tama_senior_facilities_20261029.xlsx
+++ b/data/tama_senior_facilities_20261029.xlsx
@@ -848,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y100"/>
+  <dimension ref="A1:AD100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -869,13 +869,14 @@
     <col width="72" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1012,10 +1013,15 @@
       </c>
       <c r="X5" s="13" t="inlineStr">
         <is>
+          <t>電話確認済み</t>
+        </is>
+      </c>
+      <c r="Y5" s="13" t="inlineStr">
+        <is>
           <t>メモ</t>
         </is>
       </c>
-      <c r="Y5" s="13" t="inlineStr">
+      <c r="Z5" s="13" t="inlineStr">
         <is>
           <t>記録更新日時</t>
         </is>
